--- a/services/integrator/internal/document/testdata/kartu-stok-kolom-olah.golden.xlsx
+++ b/services/integrator/internal/document/testdata/kartu-stok-kolom-olah.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">Kopi Arabika</t>
@@ -266,18 +269,18 @@
         <v>0</v>
       </c>
       <c r="C10" s="7">
-        <v>9.666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7">
         <v>0</v>
       </c>
       <c r="C11" s="7">
-        <v>0</v>
+        <v>9.666</v>
       </c>
     </row>
     <row r="12">
@@ -288,7 +291,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -299,7 +302,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="7">
-        <v>1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -310,7 +313,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -321,7 +324,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="7">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -332,7 +335,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="17">
@@ -343,7 +346,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
@@ -354,7 +357,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
     </row>
     <row r="19">
@@ -365,23 +368,34 @@
         <v>0</v>
       </c>
       <c r="C19" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9">
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9">
         <v>7.375</v>
       </c>
-      <c r="C20" s="9">
-        <v>132.416</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>20</v>
+      <c r="C21" s="9">
+        <v>132.916</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
